--- a/lorenzo-playwright-kdf/excelFramework/testcases/EC/LSTP_EC_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/EC/LSTP_EC_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\EC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E29159-687D-4A12-B2E4-973AED578E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE967F-CCDC-4839-A22F-76D616C8A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{C8B701AC-5317-4E08-91EF-D2A0B2041E7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C8B701AC-5317-4E08-91EF-D2A0B2041E7E}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="400">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login with valid credentials</t>
@@ -1699,25 +1696,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1725,13 +1719,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1739,10 +1733,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1753,16 +1747,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1770,13 +1764,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1784,16 +1778,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1801,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1815,19 +1809,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1835,16 +1829,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1852,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1866,10 +1860,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1880,16 +1874,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1897,13 +1891,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
         <v>42</v>
       </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1911,13 +1905,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
         <v>44</v>
       </c>
-      <c r="F16" t="s">
+      <c r="J16" t="s">
         <v>45</v>
-      </c>
-      <c r="J16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1925,19 +1919,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>48</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>49</v>
-      </c>
-      <c r="J17" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1945,16 +1939,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1962,13 +1956,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1976,16 +1970,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>55</v>
       </c>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1993,13 +1987,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2007,19 +2001,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
         <v>58</v>
       </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" t="s">
         <v>59</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2027,19 +2021,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>62</v>
       </c>
-      <c r="F23" t="s">
+      <c r="K23" t="s">
         <v>63</v>
-      </c>
-      <c r="K23" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -2047,16 +2041,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
         <v>65</v>
       </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" t="s">
-        <v>66</v>
-      </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -2064,13 +2058,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
-        <v>68</v>
-      </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2078,16 +2072,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
         <v>69</v>
       </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>70</v>
-      </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -2095,13 +2089,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2109,16 +2103,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
         <v>73</v>
       </c>
-      <c r="C28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -2126,13 +2120,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s">
         <v>75</v>
       </c>
-      <c r="C29" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2140,22 +2134,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" t="s">
         <v>77</v>
       </c>
-      <c r="C30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>78</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>79</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>80</v>
-      </c>
-      <c r="H30" t="s">
-        <v>81</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
@@ -2166,10 +2160,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2180,19 +2174,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" t="s">
         <v>83</v>
       </c>
-      <c r="C32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>48</v>
+      </c>
+      <c r="K32" t="s">
         <v>84</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2200,19 +2194,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" t="s">
         <v>86</v>
       </c>
-      <c r="C33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" t="s">
         <v>87</v>
-      </c>
-      <c r="F33" t="s">
-        <v>49</v>
-      </c>
-      <c r="K33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2220,19 +2214,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" t="s">
         <v>89</v>
       </c>
-      <c r="C34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
+        <v>62</v>
+      </c>
+      <c r="K34" t="s">
         <v>90</v>
-      </c>
-      <c r="F34" t="s">
-        <v>63</v>
-      </c>
-      <c r="K34" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2240,16 +2234,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" t="s">
         <v>92</v>
       </c>
-      <c r="C35" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>93</v>
-      </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2257,13 +2251,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
         <v>94</v>
       </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2271,19 +2265,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
         <v>96</v>
       </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
+        <v>48</v>
+      </c>
+      <c r="K37" t="s">
         <v>97</v>
-      </c>
-      <c r="F37" t="s">
-        <v>49</v>
-      </c>
-      <c r="K37" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2291,19 +2285,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
         <v>99</v>
       </c>
-      <c r="C38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="K38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>49</v>
-      </c>
-      <c r="K38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2311,16 +2305,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
         <v>102</v>
       </c>
-      <c r="C39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" t="s">
-        <v>103</v>
-      </c>
       <c r="F39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2328,13 +2322,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2342,16 +2336,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2359,13 +2353,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2373,19 +2367,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" t="s">
         <v>107</v>
       </c>
-      <c r="C43" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="F43" t="s">
+        <v>62</v>
+      </c>
+      <c r="K43" t="s">
         <v>108</v>
-      </c>
-      <c r="F43" t="s">
-        <v>63</v>
-      </c>
-      <c r="K43" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2393,19 +2387,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" t="s">
         <v>110</v>
       </c>
-      <c r="C44" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
+        <v>62</v>
+      </c>
+      <c r="K44" t="s">
         <v>111</v>
-      </c>
-      <c r="F44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K44" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2413,19 +2407,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" t="s">
         <v>113</v>
       </c>
-      <c r="C45" t="s">
-        <v>76</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
+        <v>62</v>
+      </c>
+      <c r="K45" t="s">
         <v>114</v>
-      </c>
-      <c r="F45" t="s">
-        <v>63</v>
-      </c>
-      <c r="K45" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2433,19 +2427,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" t="s">
         <v>116</v>
       </c>
-      <c r="C46" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
+        <v>62</v>
+      </c>
+      <c r="K46" t="s">
         <v>117</v>
-      </c>
-      <c r="F46" t="s">
-        <v>63</v>
-      </c>
-      <c r="K46" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2453,16 +2447,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" t="s">
         <v>119</v>
       </c>
-      <c r="C47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D47" t="s">
-        <v>120</v>
-      </c>
       <c r="F47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2470,13 +2464,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2484,22 +2478,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" t="s">
         <v>122</v>
       </c>
-      <c r="C49" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" t="s">
-        <v>123</v>
-      </c>
       <c r="F49" t="s">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s">
         <v>79</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>80</v>
-      </c>
-      <c r="H49" t="s">
-        <v>81</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
@@ -2510,10 +2504,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2524,19 +2518,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" t="s">
         <v>125</v>
       </c>
-      <c r="C51" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" t="s">
-        <v>126</v>
-      </c>
       <c r="F51" t="s">
+        <v>48</v>
+      </c>
+      <c r="J51" t="s">
         <v>49</v>
-      </c>
-      <c r="J51" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2544,16 +2538,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" t="s">
         <v>127</v>
       </c>
-      <c r="C52" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" t="s">
-        <v>128</v>
-      </c>
       <c r="F52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2561,13 +2555,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2575,16 +2569,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2592,13 +2586,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2606,16 +2600,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" t="s">
         <v>132</v>
       </c>
-      <c r="C56" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" t="s">
-        <v>133</v>
-      </c>
       <c r="F56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2623,13 +2617,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2637,19 +2631,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" t="s">
         <v>135</v>
       </c>
-      <c r="C58" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="F58" t="s">
+        <v>62</v>
+      </c>
+      <c r="K58" t="s">
         <v>136</v>
-      </c>
-      <c r="F58" t="s">
-        <v>63</v>
-      </c>
-      <c r="K58" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2657,19 +2651,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" t="s">
+        <v>62</v>
+      </c>
+      <c r="K59" t="s">
         <v>138</v>
-      </c>
-      <c r="C59" t="s">
-        <v>76</v>
-      </c>
-      <c r="D59" t="s">
-        <v>90</v>
-      </c>
-      <c r="F59" t="s">
-        <v>63</v>
-      </c>
-      <c r="K59" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2677,16 +2671,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2694,13 +2688,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2708,22 +2702,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F62" t="s">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s">
         <v>79</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>80</v>
-      </c>
-      <c r="H62" t="s">
-        <v>81</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
@@ -2734,10 +2728,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -2748,19 +2742,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>48</v>
+      </c>
+      <c r="J64" t="s">
         <v>49</v>
-      </c>
-      <c r="J64" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2768,16 +2762,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2785,13 +2779,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2799,16 +2793,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2816,13 +2810,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2830,16 +2824,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
         <v>149</v>
       </c>
-      <c r="C69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" t="s">
-        <v>150</v>
-      </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2847,13 +2841,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" t="s">
         <v>151</v>
       </c>
-      <c r="C70" t="s">
-        <v>152</v>
-      </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2861,16 +2855,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" t="s">
         <v>153</v>
       </c>
-      <c r="C71" t="s">
-        <v>152</v>
-      </c>
-      <c r="D71" t="s">
-        <v>154</v>
-      </c>
       <c r="F71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2878,13 +2872,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
         <v>155</v>
       </c>
-      <c r="C72" t="s">
-        <v>156</v>
-      </c>
       <c r="F72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -2892,19 +2886,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" t="s">
         <v>157</v>
       </c>
-      <c r="C73" t="s">
-        <v>156</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+      <c r="K73" t="s">
         <v>158</v>
-      </c>
-      <c r="F73" t="s">
-        <v>49</v>
-      </c>
-      <c r="K73" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2912,16 +2906,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" t="s">
         <v>160</v>
       </c>
-      <c r="C74" t="s">
-        <v>156</v>
-      </c>
-      <c r="D74" t="s">
-        <v>161</v>
-      </c>
       <c r="F74" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2929,13 +2923,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2943,16 +2937,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2960,13 +2954,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2974,16 +2968,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" t="s">
+        <v>151</v>
+      </c>
+      <c r="D78" t="s">
         <v>165</v>
       </c>
-      <c r="C78" t="s">
-        <v>152</v>
-      </c>
-      <c r="D78" t="s">
-        <v>166</v>
-      </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2991,13 +2985,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -3005,19 +2999,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
+        <v>96</v>
+      </c>
+      <c r="F80" t="s">
+        <v>48</v>
+      </c>
+      <c r="K80" t="s">
         <v>97</v>
-      </c>
-      <c r="F80" t="s">
-        <v>49</v>
-      </c>
-      <c r="K80" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -3025,19 +3019,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D81" t="s">
+        <v>99</v>
+      </c>
+      <c r="F81" t="s">
+        <v>48</v>
+      </c>
+      <c r="K81" t="s">
         <v>100</v>
-      </c>
-      <c r="F81" t="s">
-        <v>49</v>
-      </c>
-      <c r="K81" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -3045,16 +3039,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -3062,13 +3056,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -3076,16 +3070,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D84" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F84" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -3093,13 +3087,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -3107,19 +3101,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" t="s">
+        <v>151</v>
+      </c>
+      <c r="D86" t="s">
         <v>174</v>
       </c>
-      <c r="C86" t="s">
-        <v>152</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="F86" t="s">
+        <v>48</v>
+      </c>
+      <c r="K86" t="s">
         <v>175</v>
-      </c>
-      <c r="F86" t="s">
-        <v>49</v>
-      </c>
-      <c r="K86" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -3127,19 +3121,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87" t="s">
         <v>177</v>
       </c>
-      <c r="C87" t="s">
-        <v>152</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="F87" t="s">
+        <v>62</v>
+      </c>
+      <c r="K87" t="s">
         <v>178</v>
-      </c>
-      <c r="F87" t="s">
-        <v>63</v>
-      </c>
-      <c r="K87" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -3147,16 +3141,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D88" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -3164,13 +3158,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -3178,22 +3172,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F90" t="s">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s">
         <v>79</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>80</v>
-      </c>
-      <c r="H90" t="s">
-        <v>81</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
@@ -3204,10 +3198,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -3218,19 +3212,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
+        <v>48</v>
+      </c>
+      <c r="J92" t="s">
         <v>49</v>
-      </c>
-      <c r="J92" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -3238,16 +3232,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -3255,13 +3249,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3269,16 +3263,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C95" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D95" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F95" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3286,13 +3280,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3300,16 +3294,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" t="s">
+        <v>23</v>
+      </c>
+      <c r="D97" t="s">
         <v>187</v>
       </c>
-      <c r="C97" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" t="s">
-        <v>188</v>
-      </c>
       <c r="F97" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -3317,13 +3311,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3331,19 +3325,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>189</v>
+      </c>
+      <c r="C99" t="s">
+        <v>151</v>
+      </c>
+      <c r="D99" t="s">
         <v>190</v>
       </c>
-      <c r="C99" t="s">
-        <v>152</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
+        <v>62</v>
+      </c>
+      <c r="K99" t="s">
         <v>191</v>
-      </c>
-      <c r="F99" t="s">
-        <v>63</v>
-      </c>
-      <c r="K99" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -3351,19 +3345,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" t="s">
+        <v>151</v>
+      </c>
+      <c r="D100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F100" t="s">
+        <v>62</v>
+      </c>
+      <c r="K100" t="s">
         <v>193</v>
-      </c>
-      <c r="C100" t="s">
-        <v>152</v>
-      </c>
-      <c r="D100" t="s">
-        <v>136</v>
-      </c>
-      <c r="F100" t="s">
-        <v>63</v>
-      </c>
-      <c r="K100" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -3371,16 +3365,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3388,13 +3382,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -3402,22 +3396,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F103" t="s">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s">
         <v>79</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>80</v>
-      </c>
-      <c r="H103" t="s">
-        <v>81</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
@@ -3428,10 +3422,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3442,19 +3436,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D105" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" t="s">
+        <v>48</v>
+      </c>
+      <c r="J105" t="s">
         <v>49</v>
-      </c>
-      <c r="J105" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -3462,16 +3456,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D106" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3479,13 +3473,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -3493,16 +3487,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D108" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -3510,13 +3504,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -3524,16 +3518,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>201</v>
+      </c>
+      <c r="C110" t="s">
+        <v>23</v>
+      </c>
+      <c r="D110" t="s">
         <v>202</v>
       </c>
-      <c r="C110" t="s">
-        <v>24</v>
-      </c>
-      <c r="D110" t="s">
-        <v>203</v>
-      </c>
       <c r="F110" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -3541,13 +3535,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>203</v>
+      </c>
+      <c r="C111" t="s">
         <v>204</v>
       </c>
-      <c r="C111" t="s">
-        <v>205</v>
-      </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -3555,16 +3549,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112" t="s">
+        <v>204</v>
+      </c>
+      <c r="D112" t="s">
         <v>206</v>
       </c>
-      <c r="C112" t="s">
-        <v>205</v>
-      </c>
-      <c r="D112" t="s">
-        <v>207</v>
-      </c>
       <c r="F112" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -3572,13 +3566,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -3586,19 +3580,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D114" t="s">
+        <v>96</v>
+      </c>
+      <c r="F114" t="s">
+        <v>48</v>
+      </c>
+      <c r="K114" t="s">
         <v>97</v>
-      </c>
-      <c r="F114" t="s">
-        <v>49</v>
-      </c>
-      <c r="K114" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -3606,19 +3600,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D115" t="s">
+        <v>99</v>
+      </c>
+      <c r="F115" t="s">
+        <v>48</v>
+      </c>
+      <c r="K115" t="s">
         <v>100</v>
-      </c>
-      <c r="F115" t="s">
-        <v>49</v>
-      </c>
-      <c r="K115" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -3626,16 +3620,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C116" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D116" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -3643,13 +3637,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C117" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -3657,16 +3651,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C118" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3674,13 +3668,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C119" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -3688,19 +3682,19 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>214</v>
+      </c>
+      <c r="C120" t="s">
+        <v>204</v>
+      </c>
+      <c r="D120" t="s">
         <v>215</v>
       </c>
-      <c r="C120" t="s">
-        <v>205</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="F120" t="s">
+        <v>48</v>
+      </c>
+      <c r="K120" t="s">
         <v>216</v>
-      </c>
-      <c r="F120" t="s">
-        <v>49</v>
-      </c>
-      <c r="K120" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -3708,16 +3702,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C121" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D121" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -3725,13 +3719,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C122" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -3739,22 +3733,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F123" t="s">
+        <v>78</v>
+      </c>
+      <c r="G123" t="s">
         <v>79</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>80</v>
-      </c>
-      <c r="H123" t="s">
-        <v>81</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
@@ -3765,10 +3759,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F124" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -3779,19 +3773,19 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D125" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F125" t="s">
+        <v>48</v>
+      </c>
+      <c r="J125" t="s">
         <v>49</v>
-      </c>
-      <c r="J125" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -3799,16 +3793,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C126" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D126" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -3816,13 +3810,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C127" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -3830,16 +3824,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C128" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D128" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F128" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -3847,13 +3841,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -3861,16 +3855,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
+        <v>225</v>
+      </c>
+      <c r="C130" t="s">
+        <v>23</v>
+      </c>
+      <c r="D130" t="s">
         <v>226</v>
       </c>
-      <c r="C130" t="s">
-        <v>24</v>
-      </c>
-      <c r="D130" t="s">
-        <v>227</v>
-      </c>
       <c r="F130" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -3878,13 +3872,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
+        <v>227</v>
+      </c>
+      <c r="C131" t="s">
         <v>228</v>
       </c>
-      <c r="C131" t="s">
-        <v>229</v>
-      </c>
       <c r="F131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -3892,19 +3886,19 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>229</v>
+      </c>
+      <c r="C132" t="s">
+        <v>228</v>
+      </c>
+      <c r="D132" t="s">
         <v>230</v>
       </c>
-      <c r="C132" t="s">
-        <v>229</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="F132" t="s">
+        <v>48</v>
+      </c>
+      <c r="K132" t="s">
         <v>231</v>
-      </c>
-      <c r="F132" t="s">
-        <v>49</v>
-      </c>
-      <c r="K132" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -3912,16 +3906,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>232</v>
+      </c>
+      <c r="C133" t="s">
+        <v>228</v>
+      </c>
+      <c r="D133" t="s">
         <v>233</v>
       </c>
-      <c r="C133" t="s">
-        <v>229</v>
-      </c>
-      <c r="D133" t="s">
-        <v>234</v>
-      </c>
       <c r="F133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -3929,13 +3923,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C134" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F134" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -3943,19 +3937,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C135" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D135" t="s">
+        <v>96</v>
+      </c>
+      <c r="F135" t="s">
+        <v>48</v>
+      </c>
+      <c r="K135" t="s">
         <v>97</v>
-      </c>
-      <c r="F135" t="s">
-        <v>49</v>
-      </c>
-      <c r="K135" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -3963,19 +3957,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D136" t="s">
+        <v>99</v>
+      </c>
+      <c r="F136" t="s">
+        <v>48</v>
+      </c>
+      <c r="K136" t="s">
         <v>100</v>
-      </c>
-      <c r="F136" t="s">
-        <v>49</v>
-      </c>
-      <c r="K136" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -3983,16 +3977,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D137" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -4000,13 +3994,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -4014,16 +4008,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F139" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -4031,13 +4025,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F140" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -4045,19 +4039,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
+        <v>241</v>
+      </c>
+      <c r="C141" t="s">
+        <v>228</v>
+      </c>
+      <c r="D141" t="s">
         <v>242</v>
       </c>
-      <c r="C141" t="s">
-        <v>229</v>
-      </c>
-      <c r="D141" t="s">
+      <c r="F141" t="s">
+        <v>62</v>
+      </c>
+      <c r="K141" t="s">
         <v>243</v>
-      </c>
-      <c r="F141" t="s">
-        <v>63</v>
-      </c>
-      <c r="K141" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -4065,19 +4059,19 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
+        <v>244</v>
+      </c>
+      <c r="C142" t="s">
+        <v>228</v>
+      </c>
+      <c r="D142" t="s">
         <v>245</v>
       </c>
-      <c r="C142" t="s">
-        <v>229</v>
-      </c>
-      <c r="D142" t="s">
+      <c r="F142" t="s">
+        <v>62</v>
+      </c>
+      <c r="K142" t="s">
         <v>246</v>
-      </c>
-      <c r="F142" t="s">
-        <v>63</v>
-      </c>
-      <c r="K142" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -4085,16 +4079,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>247</v>
+      </c>
+      <c r="C143" t="s">
+        <v>228</v>
+      </c>
+      <c r="D143" t="s">
         <v>248</v>
       </c>
-      <c r="C143" t="s">
-        <v>229</v>
-      </c>
-      <c r="D143" t="s">
-        <v>249</v>
-      </c>
       <c r="F143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -4102,13 +4096,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F144" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -4116,19 +4110,19 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
+        <v>250</v>
+      </c>
+      <c r="C145" t="s">
+        <v>94</v>
+      </c>
+      <c r="D145" t="s">
         <v>251</v>
       </c>
-      <c r="C145" t="s">
-        <v>95</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="F145" t="s">
+        <v>48</v>
+      </c>
+      <c r="K145" t="s">
         <v>252</v>
-      </c>
-      <c r="F145" t="s">
-        <v>49</v>
-      </c>
-      <c r="K145" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -4136,16 +4130,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C146" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -4153,13 +4147,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F147" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -4167,16 +4161,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C148" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -4184,13 +4178,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C149" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -4198,16 +4192,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C150" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D150" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -4215,13 +4209,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C151" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F151" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -4229,16 +4223,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>259</v>
+      </c>
+      <c r="C152" t="s">
+        <v>71</v>
+      </c>
+      <c r="D152" t="s">
         <v>260</v>
       </c>
-      <c r="C152" t="s">
-        <v>72</v>
-      </c>
-      <c r="D152" t="s">
-        <v>261</v>
-      </c>
       <c r="F152" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -4246,13 +4240,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
+        <v>261</v>
+      </c>
+      <c r="C153" t="s">
         <v>262</v>
       </c>
-      <c r="C153" t="s">
-        <v>263</v>
-      </c>
       <c r="F153" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -4260,16 +4254,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>263</v>
+      </c>
+      <c r="C154" t="s">
+        <v>262</v>
+      </c>
+      <c r="D154" t="s">
         <v>264</v>
       </c>
-      <c r="C154" t="s">
-        <v>263</v>
-      </c>
-      <c r="D154" t="s">
-        <v>265</v>
-      </c>
       <c r="F154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -4277,13 +4271,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C155" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F155" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -4291,19 +4285,19 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C156" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D156" t="s">
+        <v>96</v>
+      </c>
+      <c r="F156" t="s">
+        <v>48</v>
+      </c>
+      <c r="K156" t="s">
         <v>97</v>
-      </c>
-      <c r="F156" t="s">
-        <v>49</v>
-      </c>
-      <c r="K156" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -4311,19 +4305,19 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D157" t="s">
+        <v>99</v>
+      </c>
+      <c r="F157" t="s">
+        <v>48</v>
+      </c>
+      <c r="K157" t="s">
         <v>100</v>
-      </c>
-      <c r="F157" t="s">
-        <v>49</v>
-      </c>
-      <c r="K157" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -4331,16 +4325,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C158" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D158" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F158" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -4348,13 +4342,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F159" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -4362,16 +4356,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C160" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F160" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -4379,13 +4373,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C161" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F161" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -4393,19 +4387,19 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>272</v>
+      </c>
+      <c r="C162" t="s">
+        <v>262</v>
+      </c>
+      <c r="D162" t="s">
         <v>273</v>
       </c>
-      <c r="C162" t="s">
-        <v>263</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
+        <v>62</v>
+      </c>
+      <c r="K162" t="s">
         <v>274</v>
-      </c>
-      <c r="F162" t="s">
-        <v>63</v>
-      </c>
-      <c r="K162" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -4413,16 +4407,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C163" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F163" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -4430,13 +4424,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C164" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F164" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -4444,22 +4438,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C165" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D165" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F165" t="s">
+        <v>78</v>
+      </c>
+      <c r="G165" t="s">
         <v>79</v>
       </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>80</v>
-      </c>
-      <c r="H165" t="s">
-        <v>81</v>
       </c>
       <c r="J165" t="b">
         <v>1</v>
@@ -4470,10 +4464,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -4484,16 +4478,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>279</v>
+      </c>
+      <c r="C167" t="s">
+        <v>23</v>
+      </c>
+      <c r="D167" t="s">
         <v>280</v>
       </c>
-      <c r="C167" t="s">
-        <v>24</v>
-      </c>
-      <c r="D167" t="s">
-        <v>281</v>
-      </c>
       <c r="F167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -4501,13 +4495,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C168" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F168" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -4515,16 +4509,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
+        <v>282</v>
+      </c>
+      <c r="C169" t="s">
+        <v>155</v>
+      </c>
+      <c r="D169" t="s">
         <v>283</v>
       </c>
-      <c r="C169" t="s">
-        <v>156</v>
-      </c>
-      <c r="D169" t="s">
-        <v>284</v>
-      </c>
       <c r="F169" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -4532,13 +4526,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C170" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F170" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -4546,22 +4540,22 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C171" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D171" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F171" t="s">
+        <v>78</v>
+      </c>
+      <c r="G171" t="s">
         <v>79</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>80</v>
-      </c>
-      <c r="H171" t="s">
-        <v>81</v>
       </c>
       <c r="J171" t="b">
         <v>1</v>
@@ -4572,10 +4566,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F172" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J172">
         <v>1</v>
@@ -4586,16 +4580,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C173" t="s">
+        <v>23</v>
+      </c>
+      <c r="D173" t="s">
         <v>24</v>
       </c>
-      <c r="D173" t="s">
-        <v>25</v>
-      </c>
       <c r="F173" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -4603,13 +4597,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C174" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F174" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -4617,16 +4611,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C175" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D175" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F175" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -4634,13 +4628,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>29</v>
+      </c>
+      <c r="C176" t="s">
         <v>30</v>
       </c>
-      <c r="C176" t="s">
-        <v>31</v>
-      </c>
       <c r="F176" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -4648,19 +4642,19 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C177" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D177" t="s">
+        <v>32</v>
+      </c>
+      <c r="E177" t="s">
         <v>33</v>
       </c>
-      <c r="E177" t="s">
-        <v>34</v>
-      </c>
       <c r="F177" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -4668,16 +4662,16 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C178" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D178" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -4685,13 +4679,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C179" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -4699,19 +4693,19 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C180" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D180" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F180" t="s">
+        <v>48</v>
+      </c>
+      <c r="J180" t="s">
         <v>49</v>
-      </c>
-      <c r="J180" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -4719,16 +4713,16 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C181" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D181" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F181" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -4736,13 +4730,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C182" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F182" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -4750,16 +4744,16 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C183" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F183" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -4767,13 +4761,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C184" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F184" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -4781,10 +4775,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F185" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J185">
         <v>1</v>
@@ -4795,16 +4789,16 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>298</v>
+      </c>
+      <c r="C186" t="s">
+        <v>23</v>
+      </c>
+      <c r="D186" t="s">
         <v>299</v>
       </c>
-      <c r="C186" t="s">
-        <v>24</v>
-      </c>
-      <c r="D186" t="s">
-        <v>300</v>
-      </c>
       <c r="F186" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -4812,13 +4806,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>300</v>
+      </c>
+      <c r="C187" t="s">
         <v>301</v>
       </c>
-      <c r="C187" t="s">
-        <v>302</v>
-      </c>
       <c r="F187" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -4826,19 +4820,19 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>302</v>
+      </c>
+      <c r="C188" t="s">
+        <v>301</v>
+      </c>
+      <c r="D188" t="s">
         <v>303</v>
       </c>
-      <c r="C188" t="s">
-        <v>302</v>
-      </c>
-      <c r="D188" t="s">
+      <c r="F188" t="s">
+        <v>48</v>
+      </c>
+      <c r="K188" t="s">
         <v>304</v>
-      </c>
-      <c r="F188" t="s">
-        <v>49</v>
-      </c>
-      <c r="K188" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -4846,16 +4840,16 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>305</v>
+      </c>
+      <c r="C189" t="s">
+        <v>301</v>
+      </c>
+      <c r="D189" t="s">
         <v>306</v>
       </c>
-      <c r="C189" t="s">
-        <v>302</v>
-      </c>
-      <c r="D189" t="s">
-        <v>307</v>
-      </c>
       <c r="F189" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -4863,13 +4857,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C190" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F190" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -4877,19 +4871,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C191" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D191" t="s">
+        <v>96</v>
+      </c>
+      <c r="F191" t="s">
+        <v>48</v>
+      </c>
+      <c r="K191" t="s">
         <v>97</v>
-      </c>
-      <c r="F191" t="s">
-        <v>49</v>
-      </c>
-      <c r="K191" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -4897,19 +4891,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C192" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D192" t="s">
+        <v>99</v>
+      </c>
+      <c r="F192" t="s">
+        <v>48</v>
+      </c>
+      <c r="K192" t="s">
         <v>100</v>
-      </c>
-      <c r="F192" t="s">
-        <v>49</v>
-      </c>
-      <c r="K192" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -4917,16 +4911,16 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C193" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D193" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F193" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -4934,13 +4928,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C194" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F194" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -4948,16 +4942,16 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C195" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F195" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -4965,13 +4959,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C196" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F196" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -4979,16 +4973,16 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>314</v>
+      </c>
+      <c r="C197" t="s">
+        <v>301</v>
+      </c>
+      <c r="D197" t="s">
         <v>315</v>
       </c>
-      <c r="C197" t="s">
-        <v>302</v>
-      </c>
-      <c r="D197" t="s">
-        <v>316</v>
-      </c>
       <c r="F197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -4996,13 +4990,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C198" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F198" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -5010,19 +5004,19 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
+        <v>317</v>
+      </c>
+      <c r="C199" t="s">
+        <v>301</v>
+      </c>
+      <c r="D199" t="s">
         <v>318</v>
       </c>
-      <c r="C199" t="s">
-        <v>302</v>
-      </c>
-      <c r="D199" t="s">
+      <c r="F199" t="s">
+        <v>48</v>
+      </c>
+      <c r="K199" t="s">
         <v>319</v>
-      </c>
-      <c r="F199" t="s">
-        <v>49</v>
-      </c>
-      <c r="K199" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -5030,19 +5024,19 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
+        <v>320</v>
+      </c>
+      <c r="C200" t="s">
+        <v>301</v>
+      </c>
+      <c r="D200" t="s">
         <v>321</v>
       </c>
-      <c r="C200" t="s">
-        <v>302</v>
-      </c>
-      <c r="D200" t="s">
+      <c r="F200" t="s">
+        <v>62</v>
+      </c>
+      <c r="K200" t="s">
         <v>322</v>
-      </c>
-      <c r="F200" t="s">
-        <v>63</v>
-      </c>
-      <c r="K200" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -5050,19 +5044,19 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
+        <v>323</v>
+      </c>
+      <c r="C201" t="s">
+        <v>301</v>
+      </c>
+      <c r="D201" t="s">
         <v>324</v>
       </c>
-      <c r="C201" t="s">
-        <v>302</v>
-      </c>
-      <c r="D201" t="s">
+      <c r="F201" t="s">
+        <v>62</v>
+      </c>
+      <c r="K201" t="s">
         <v>325</v>
-      </c>
-      <c r="F201" t="s">
-        <v>63</v>
-      </c>
-      <c r="K201" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -5070,16 +5064,16 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
+        <v>326</v>
+      </c>
+      <c r="C202" t="s">
+        <v>301</v>
+      </c>
+      <c r="D202" t="s">
         <v>327</v>
       </c>
-      <c r="C202" t="s">
-        <v>302</v>
-      </c>
-      <c r="D202" t="s">
-        <v>328</v>
-      </c>
       <c r="F202" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -5087,13 +5081,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C203" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F203" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -5101,22 +5095,22 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C204" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D204" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F204" t="s">
+        <v>78</v>
+      </c>
+      <c r="G204" t="s">
         <v>79</v>
       </c>
-      <c r="G204" t="s">
+      <c r="H204" t="s">
         <v>80</v>
-      </c>
-      <c r="H204" t="s">
-        <v>81</v>
       </c>
       <c r="J204" t="b">
         <v>1</v>
@@ -5127,10 +5121,10 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F205" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J205">
         <v>1</v>
@@ -5141,16 +5135,16 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
+        <v>331</v>
+      </c>
+      <c r="C206" t="s">
+        <v>18</v>
+      </c>
+      <c r="D206" t="s">
         <v>332</v>
       </c>
-      <c r="C206" t="s">
-        <v>19</v>
-      </c>
-      <c r="D206" t="s">
-        <v>333</v>
-      </c>
       <c r="F206" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -5158,16 +5152,16 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
+        <v>333</v>
+      </c>
+      <c r="C207" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" t="s">
         <v>334</v>
       </c>
-      <c r="C207" t="s">
-        <v>19</v>
-      </c>
-      <c r="D207" t="s">
-        <v>335</v>
-      </c>
       <c r="F207" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -5212,144 +5206,144 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" t="s">
         <v>336</v>
-      </c>
-      <c r="B2" t="s">
-        <v>337</v>
       </c>
       <c r="C2" s="2">
         <v>46147.375</v>
       </c>
       <c r="D2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" t="s">
         <v>338</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>339</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>340</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>341</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>342</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>343</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>344</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>345</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>346</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>347</v>
-      </c>
-      <c r="N2" t="s">
-        <v>348</v>
       </c>
       <c r="O2" s="2">
         <v>46147.385416666664</v>
       </c>
       <c r="P2" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q2" t="s">
         <v>349</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>350</v>
-      </c>
-      <c r="R2" t="s">
-        <v>351</v>
       </c>
       <c r="S2" s="2">
         <v>46147.395833333336</v>
@@ -5358,16 +5352,16 @@
         <v>46147.416666666664</v>
       </c>
       <c r="U2" t="s">
+        <v>351</v>
+      </c>
+      <c r="V2" t="s">
         <v>352</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>353</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>354</v>
-      </c>
-      <c r="X2" t="s">
-        <v>355</v>
       </c>
       <c r="Y2" s="2">
         <v>46147.5</v>
@@ -5376,10 +5370,10 @@
         <v>46147.5</v>
       </c>
       <c r="AA2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB2" t="s">
         <v>356</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -5398,71 +5392,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B9" s="4">
         <v>206</v>
@@ -5470,7 +5464,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B10" s="4">
         <v>14</v>
@@ -5478,7 +5472,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B11" s="4">
         <v>48</v>
@@ -5486,15 +5480,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B13" s="5">
         <v>46147</v>
@@ -5502,7 +5496,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B14" s="5">
         <v>46147</v>
@@ -5510,31 +5504,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B18" s="4">
         <v>7</v>
@@ -5542,18 +5536,18 @@
     </row>
     <row r="19" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>389</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -5573,49 +5567,55 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
         <v>394</v>
-      </c>
-      <c r="C2" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3" t="s">
         <v>396</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>397</v>
-      </c>
-      <c r="C3" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" t="s">
         <v>399</v>
       </c>
-      <c r="B4" t="s">
-        <v>400</v>
-      </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/EC/LSTP_EC_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/EC/LSTP_EC_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\EC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE967F-CCDC-4839-A22F-76D616C8A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7B4117-EB1B-4409-9455-30A5F680D0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C8B701AC-5317-4E08-91EF-D2A0B2041E7E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="401">
   <si>
     <t>StepNo</t>
   </si>
@@ -1239,6 +1239,9 @@
   </si>
   <si>
     <t>Login password from environment configuration</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +1982,7 @@
         <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2050,7 +2053,7 @@
         <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/EC/LSTP_EC_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/EC/LSTP_EC_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\EC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7B4117-EB1B-4409-9455-30A5F680D0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274F93A7-30F1-4739-BE65-4E08BBCB65DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C8B701AC-5317-4E08-91EF-D2A0B2041E7E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="403">
   <si>
     <t>StepNo</t>
   </si>
@@ -1242,6 +1242,12 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>pageWarningLORENZO</t>
+  </si>
+  <si>
+    <t>pageDefUsers</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2084,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>401</v>
       </c>
       <c r="D26" t="s">
         <v>69</v>
@@ -2271,7 +2277,7 @@
         <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D37" t="s">
         <v>96</v>
@@ -2291,7 +2297,7 @@
         <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D38" t="s">
         <v>99</v>
@@ -2311,7 +2317,7 @@
         <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D39" t="s">
         <v>102</v>
@@ -2342,7 +2348,7 @@
         <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s">
         <v>35</v>
@@ -3005,7 +3011,7 @@
         <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D80" t="s">
         <v>96</v>
@@ -3025,7 +3031,7 @@
         <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D81" t="s">
         <v>99</v>
@@ -3045,7 +3051,7 @@
         <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D82" t="s">
         <v>102</v>
@@ -3076,7 +3082,7 @@
         <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D84" t="s">
         <v>35</v>
@@ -3586,7 +3592,7 @@
         <v>208</v>
       </c>
       <c r="C114" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D114" t="s">
         <v>96</v>
@@ -3606,7 +3612,7 @@
         <v>209</v>
       </c>
       <c r="C115" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D115" t="s">
         <v>99</v>
@@ -3626,7 +3632,7 @@
         <v>210</v>
       </c>
       <c r="C116" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D116" t="s">
         <v>102</v>
@@ -3657,7 +3663,7 @@
         <v>212</v>
       </c>
       <c r="C118" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D118" t="s">
         <v>35</v>
@@ -3943,7 +3949,7 @@
         <v>235</v>
       </c>
       <c r="C135" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D135" t="s">
         <v>96</v>
@@ -3963,7 +3969,7 @@
         <v>236</v>
       </c>
       <c r="C136" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D136" t="s">
         <v>99</v>
@@ -3983,7 +3989,7 @@
         <v>237</v>
       </c>
       <c r="C137" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D137" t="s">
         <v>102</v>
@@ -4014,7 +4020,7 @@
         <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D139" t="s">
         <v>35</v>
@@ -4116,7 +4122,7 @@
         <v>250</v>
       </c>
       <c r="C145" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D145" t="s">
         <v>251</v>
@@ -4136,7 +4142,7 @@
         <v>253</v>
       </c>
       <c r="C146" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D146" t="s">
         <v>51</v>
@@ -4167,7 +4173,7 @@
         <v>255</v>
       </c>
       <c r="C148" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D148" t="s">
         <v>35</v>
@@ -4291,7 +4297,7 @@
         <v>266</v>
       </c>
       <c r="C156" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D156" t="s">
         <v>96</v>
@@ -4311,7 +4317,7 @@
         <v>267</v>
       </c>
       <c r="C157" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D157" t="s">
         <v>99</v>
@@ -4331,7 +4337,7 @@
         <v>268</v>
       </c>
       <c r="C158" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D158" t="s">
         <v>102</v>
@@ -4362,7 +4368,7 @@
         <v>270</v>
       </c>
       <c r="C160" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D160" t="s">
         <v>35</v>
@@ -4877,7 +4883,7 @@
         <v>308</v>
       </c>
       <c r="C191" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D191" t="s">
         <v>96</v>
@@ -4897,7 +4903,7 @@
         <v>309</v>
       </c>
       <c r="C192" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D192" t="s">
         <v>99</v>
@@ -4917,7 +4923,7 @@
         <v>310</v>
       </c>
       <c r="C193" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D193" t="s">
         <v>102</v>
@@ -4948,7 +4954,7 @@
         <v>312</v>
       </c>
       <c r="C195" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="D195" t="s">
         <v>35</v>
